--- a/processed_ruby_restored_xlsx/sc121_瑠璃千代１：風呂.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc121_瑠璃千代１：風呂.ss.xlsx
@@ -884,8 +884,8 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Maybe because I got so nervous from the suddenness, my
-speech kept coming out all awkward.</t>
+          <t>Maybe because I got so nervous from the suddenness,
+my speech kept coming out all awkward.</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1500,8 +1500,8 @@
       <c r="B68" s="1" t="inlineStr">
         <is>
           <t>She looks up at the ceiling searching for the next
-thing to say… tilts her head a little to the right and
-left… and parts her lips slightly…</t>
+thing to say… tilts her head a little to the right
+and left… and parts her lips slightly…</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1841,8 +1841,8 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>That casual question from Rurichiyo-chan feels like it
-pierces my heart.</t>
+          <t>That casual question from Rurichiyo-chan feels like
+it pierces my heart.</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1934,7 +1934,8 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>「Ah… ahaha… Thank you for looking after me back then…」</t>
+          <t>「Ah… ahaha… Thank you for looking after me back
+then…」</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2301,7 +2302,8 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>「By the way… Rurichiyo-chan, you didn't do it, right?」</t>
+          <t>「By the way… Rurichiyo-chan, you didn't do it,
+right?」</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2561,8 +2563,8 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>It wasn't even a clever joke to begin with, but having
-said it I can't take it back.</t>
+          <t>It wasn't even a clever joke to begin with, but
+having said it I can't take it back.</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2823,8 +2825,8 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>「That was... something everyone back then still hadn't
-done...」</t>
+          <t>「That was... something everyone back then still
+hadn't done...」</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2931,8 +2933,9 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>You could tell even in the bath how turned on she was,
-right down to the place that was totally riled up….</t>
+          <t>You could tell even in the bath how turned on she
+was, right down to the place that was totally riled
+up….</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -3250,8 +3253,8 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>Flustered, Rurichiyo-chan kept opening and closing her
-mouth, unable to settle.</t>
+          <t>Flustered, Rurichiyo-chan kept opening and closing
+her mouth, unable to settle.</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3753,8 +3756,8 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>When I encouraged Rurichiyo-chan to come closer to me,
-she exhaled shortly and slowly moved nearer.</t>
+          <t>When I encouraged Rurichiyo-chan to come closer to
+me, she exhaled shortly and slowly moved nearer.</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3814,8 +3817,8 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>Even so, the anticipation of what I was about to teach
-her made a loud swell of arousal.</t>
+          <t>Even so, the anticipation of what I was about to
+teach her made a loud swell of arousal.</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -4028,8 +4031,8 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan nodded reflexively, but she looked like
-she had no idea what to do.</t>
+          <t>Rurichiyo-chan nodded reflexively, but she looked
+like she had no idea what to do.</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4091,7 +4094,8 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>As if in time with that, the penis pulsed and reacted.</t>
+          <t>As if in time with that, the penis pulsed and
+reacted.</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4944,8 +4948,8 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>But manga panels and real life are just too different,
-so I guess she doesn't know what to do.</t>
+          <t>But manga panels and real life are just too
+different, so I guess she doesn't know what to do.</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4960,8 +4964,8 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>...But more than that, what made me happy was the fact
-that she wanted to make me feel good.</t>
+          <t>...But more than that, what made me happy was the
+fact that she wanted to make me feel good.</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4991,8 +4995,8 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>「Today… it’s a secret, a special lesson, okay？ Even if
-it doesn’t go well, I’ll make sure to teach you
+          <t>「Today… it’s a secret, a special lesson, okay？ Even
+if it doesn’t go well, I’ll make sure to teach you
 properly.」</t>
         </is>
       </c>
@@ -5498,8 +5502,8 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>Now mixed with the feeling of saliva, the whole tip is
-wrapped in a thick, blissful sensation.</t>
+          <t>Now mixed with the feeling of saliva, the whole tip
+is wrapped in a thick, blissful sensation.</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5574,7 +5578,8 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>I couldn't help my hips jolting from how good it felt.</t>
+          <t>I couldn't help my hips jolting from how good it
+felt.</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5589,8 +5594,8 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>It must have startled Rurichiyo-chan too, what with it
-happening so suddenly.</t>
+          <t>It must have startled Rurichiyo-chan too, what with
+it happening so suddenly.</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -5931,8 +5936,8 @@
       </c>
       <c r="B357" s="1" t="inlineStr">
         <is>
-          <t>She focused more than before, giving my penis repeated
-chu, chu little stimulations.</t>
+          <t>She focused more than before, giving my penis
+repeated chu, chu little stimulations.</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -5993,8 +5998,8 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>Ugh… seeing Rurichiyo-chan’s smile, I must be making a
-ridiculous face….</t>
+          <t>Ugh… seeing Rurichiyo-chan’s smile, I must be making
+a ridiculous face….</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -6193,8 +6198,8 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan’s small mouth opened wide, and her face
-looked incredibly sexy.</t>
+          <t>Rurichiyo-chan’s small mouth opened wide, and her
+face looked incredibly sexy.</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6240,7 +6245,8 @@
       <c r="B377" s="1" t="inlineStr">
         <is>
           <t>Ooh... Rurichiyo-chan's mouth is taking my penis in,
-little by little... little by little, swallowing it...</t>
+little by little... little by little, swallowing
+it...</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -6301,7 +6307,8 @@
       <c r="B381" s="1" t="inlineStr">
         <is>
           <t>The head, made sensitive from all the kissing, gets a
-little crushed and my whole body instantly flushes...！</t>
+little crushed and my whole body instantly
+flushes...！</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -6670,8 +6677,9 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t>A drop of saliva dripped from the corner of her mouth,
-slid down the penis with a ssss~ sound and fell.</t>
+          <t>A drop of saliva dripped from the corner of her
+mouth, slid down the penis with a ssss~ sound and
+fell.</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -6732,7 +6740,8 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t>「Frenulum？ n'uh, n！ chu, chuu... chuku, chuba！ chuba！」</t>
+          <t>「Frenulum？ n'uh, n！ chu, chuu... chuku, chuba！
+chuba！」</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -6900,8 +6909,8 @@
       </c>
       <c r="B420" s="1" t="inlineStr">
         <is>
-          <t>「Yeah… I know. If you keep rubbing me like this inside
-my mouth, I’ll definitely come…」</t>
+          <t>「Yeah… I know. If you keep rubbing me like this
+inside my mouth, I’ll definitely come…」</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -7010,8 +7019,8 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>She sucks on the tip, taking me in and licking me over
-and over...</t>
+          <t>She sucks on the tip, taking me in and licking me
+over and over...</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7041,8 +7050,8 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t>「Mmm, ah...！ Your tongue's really good... ah！ Even the
-little bump at the tip...！」</t>
+          <t>「Mmm, ah...！ Your tongue's really good... ah！ Even
+the little bump at the tip...！」</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -7088,9 +7097,9 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t>She seemed to be getting more used to it, and before I
-could finish speaking she was already attacking faster
-than I could say anything.</t>
+          <t>She seemed to be getting more used to it, and before
+I could finish speaking she was already attacking
+faster than I could say anything.</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -7294,8 +7303,8 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t>By the time we got this far, there was nothing I could
-teach her.</t>
+          <t>By the time we got this far, there was nothing I
+could teach her.</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -7542,8 +7551,8 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t>Every time my penis twitches, I feel like I'm going to
-pass out.</t>
+          <t>Every time my penis twitches, I feel like I'm going
+to pass out.</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -7791,8 +7800,8 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t>A hot feeling was coming from inside... I was about to
-finish already.</t>
+          <t>A hot feeling was coming from inside... I was about
+to finish already.</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -8099,8 +8108,8 @@
       <c r="B497" s="1" t="inlineStr">
         <is>
           <t>...But maybe because my body had warmed up, my
-ejaculations still didn't seem like they were going to
-stop...</t>
+ejaculations still didn't seem like they were going
+to stop...</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -8451,8 +8460,8 @@
       </c>
       <c r="B520" s="1" t="inlineStr">
         <is>
-          <t>...I can't believe Rurichiyo-chan is going to drink my
-cum... ah...！</t>
+          <t>...I can't believe Rurichiyo-chan is going to drink
+my cum... ah...！</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -8771,8 +8780,8 @@
       </c>
       <c r="B541" s="1" t="inlineStr">
         <is>
-          <t>It was fine up until then, but the rising urge to come
-just wouldn’t stop—！</t>
+          <t>It was fine up until then, but the rising urge to
+come just wouldn’t stop—！</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -9001,8 +9010,8 @@
       </c>
       <c r="B556" s="1" t="inlineStr">
         <is>
-          <t>As if delivering a follow-up blow, the semen swells in
-amount and spills out even more.</t>
+          <t>As if delivering a follow-up blow, the semen swells
+in amount and spills out even more.</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -9447,8 +9456,8 @@
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
-          <t>She eased her pleasure-quivering hips slowly down into
-the bath after feeling so good from my mouth…</t>
+          <t>She eased her pleasure-quivering hips slowly down
+into the bath after feeling so good from my mouth…</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -9493,7 +9502,8 @@
       </c>
       <c r="B588" s="1" t="inlineStr">
         <is>
-          <t>I leaned back against the tub, going limp and sighing.</t>
+          <t>I leaned back against the tub, going limp and
+sighing.</t>
         </is>
       </c>
       <c r="C588" t="n">
@@ -9523,8 +9533,8 @@
       </c>
       <c r="B590" s="1" t="inlineStr">
         <is>
-          <t>「Hehe… I'm happier than anything to have made Oji-sama
-feel good…！」</t>
+          <t>「Hehe… I'm happier than anything to have made
+Oji-sama feel good…！」</t>
         </is>
       </c>
       <c r="C590" t="n">
@@ -9664,8 +9674,8 @@
       </c>
       <c r="B599" s="1" t="inlineStr">
         <is>
-          <t>But once she says that, there's nothing I can do about
-it.</t>
+          <t>But once she says that, there's nothing I can do
+about it.</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -9756,8 +9766,8 @@
       </c>
       <c r="B605" s="1" t="inlineStr">
         <is>
-          <t>Then Rurichiyo-chan loosened her cheeks into a wistful
-expression.</t>
+          <t>Then Rurichiyo-chan loosened her cheeks into a
+wistful expression.</t>
         </is>
       </c>
       <c r="C605" t="n">

--- a/processed_ruby_restored_xlsx/sc121_瑠璃千代１：風呂.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc121_瑠璃千代１：風呂.ss.xlsx
@@ -977,7 +977,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes... well then...」</t>
+          <t>Y-yes... well then...</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>「I-Is this... all right...？」</t>
+          <t>I-Is this... all right...？</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ahh！ Um, um... well...」</t>
+          <t>Ah... ahh！ Um, um... well...</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>「Ah, y-yes... if Oji-sama says I want me to do
+          <t>「Ah, y-yes... if Oji-sama says he wants me to do
 that...」</t>
         </is>
       </c>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>「Nnngggghhh... nngghh...？ Ah, u, uuu... e... um...」</t>
+          <t>Nnngggghhh... nngghh...？ Ah, u, uuu... e... um...</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>I seem a little unsure what to do.</t>
+          <t>He seems a little unsure what to do.</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4949,7 +4949,7 @@
       <c r="B293" s="1" t="inlineStr">
         <is>
           <t>But manga panels and real life are just too
-different, so I guess she doesn't know what to do.</t>
+different, so I guess they don't know what to do.</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4965,7 +4965,7 @@
       <c r="B294" s="1" t="inlineStr">
         <is>
           <t>...But more than that, what made me happy was the
-fact that she wanted to make me feel good.</t>
+fact that they wanted to make me feel good.</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... Oji-sama？ Are you... okay？」</t>
+          <t>Mmm... Oji-sama？ Are you... okay？</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -6957,8 +6957,8 @@
       <c r="B423" s="1" t="inlineStr">
         <is>
           <t>Maybe because she hadn't done it before, when she
-makes me ejaculate she's aware of it, and it seems to
-flip a switch in her.</t>
+makes him ejaculate she's aware of it, and it seems
+to flip a switch in her.</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -6973,8 +6973,8 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>She takes me back into her mouth and begins reviewing
-what she just did.</t>
+          <t>She takes him back into her mouth and begins
+reviewing what they just did.</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>She sucks on the tip, taking me in and licking me
+          <t>She sucks on the tip, taking him in and licking him
 over and over...</t>
         </is>
       </c>
@@ -7582,8 +7582,8 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>「chu, chu… chu！  pero, pe… ro, chuu… amu, hamuu… ha,
-mumu…」</t>
+          <t>chu, chu… chu！  pero, pe… ro, chuu… amu, hamuu… ha,
+mumu…</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t>Far from just doing what I taught, she twists her
+          <t>Far from just doing what I taught, they twist their
 tongue even more, licking up and down and left and
 right.</t>
         </is>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>「Ohi... ha, ma？ Nn, nn... nn？ Amu, chu, chuu！」</t>
+          <t>Ohi... ha, ma？ Nn, nn... nn？ Amu, chu, chuu！</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7908,8 +7908,8 @@
       </c>
       <c r="B484" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ahhhh！ It's coming out...！ Ahhh, haaah, ah！ Ah,
-aaaah！」</t>
+          <t>Ah, ahhhh！ It's coming out...！ Ahhh, haaah, ah！ Ah,
+aaaah！</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>「Nfufuuuu！　Nnngh！　Nfuu...！？」</t>
+          <t>Nfufuuuu！　Nnngh！　Nfuu...！？</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t>My penis was twitching, and you could see semen
+          <t>His penis was twitching, and you could see semen
 gushing out forcefully.</t>
         </is>
       </c>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>「Nn, gok... kok, kokuu... fua, fuaa...」</t>
+          <t>Nn, gok... kok, kokuu... fua, fuaa...</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="B539" s="1" t="inlineStr">
         <is>
-          <t>「Puhah！  Eh, ah！  Ahf, uuh…！」</t>
+          <t>Puhah！  Eh, ah！  Ahf, uuh…！</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="B559" s="1" t="inlineStr">
         <is>
-          <t>「Huh！ Fwaa, fwaa...」</t>
+          <t>Huh！ Fwaa, fwaa...</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="B562" s="1" t="inlineStr">
         <is>
-          <t>「Ah—ah！　Sorry…！」</t>
+          <t>Ah—ah！　Sorry…！</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -9457,7 +9457,7 @@
       <c r="B585" s="1" t="inlineStr">
         <is>
           <t>She eased her pleasure-quivering hips slowly down
-into the bath after feeling so good from my mouth…</t>
+into the bath after feeling so good from his mouth…</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="B588" s="1" t="inlineStr">
         <is>
-          <t>I leaned back against the tub, going limp and
+          <t>He leaned back against the tub, going limp and
 sighing.</t>
         </is>
       </c>
